--- a/design/space_dog_racing_economy.xlsx
+++ b/design/space_dog_racing_economy.xlsx
@@ -29,7 +29,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -110,6 +110,9 @@
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -171,7 +174,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -431,6 +434,7 @@
     <xf numFmtId="2" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -872,7 +876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="42" customWidth="1" style="43" min="1" max="1"/>
@@ -1638,6 +1642,153 @@
       <c r="B57" s="50" t="n"/>
       <c r="C57" s="50" t="n"/>
       <c r="D57" s="50" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="87" t="inlineStr">
+        <is>
+          <t>Race simulation (GDD §6.2 — the v2 rebalance, 11 September 2026)</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Rebalanced so all four stats matter: measured +10-to-one-stat win rates move from speed 28.8 / stam 16.7 / accel 14.4 / trap 14.0 to rating-weight order, and track length starts to matter at all. D12.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Race: base speed (m/s)</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Was 13. The floor every dog runs at before its Speed stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Race: speed coefficient (m/s per 100 Speed)</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Was 6. Cutting this is what stops the race being a pure Speed contest</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Race: fade penalty past the stamina point</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Was 0.35. Makes Stamina the second-biggest stat, and biggest on a stayer</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Race: acceleration base (m/s²)</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Was 4. Less free acceleration, so the stat buys more</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Race: acceleration coefficient (m/s² per 100 Accel)</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Was 6. Accel now peaks on the 350 m sprints</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Race: break from the boxes (metres at 100 Trap)</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>7</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Was 3. Trap craft has to be worth something out of the gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Race: bump chance on a bend</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Was 0.10. The other half of what Trap buys</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Race: bump speed penalty</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Was 0.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Race: bump distance (metres)</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Was 0.6. Dogs this close on a bend may clash</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>

--- a/design/space_dog_racing_economy.xlsx
+++ b/design/space_dog_racing_economy.xlsx
@@ -876,7 +876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D72"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="42" customWidth="1" style="43" min="1" max="1"/>
@@ -1798,32 +1798,218 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="43" t="inlineStr">
         <is>
           <t>Fitness multiplier: floor</t>
         </is>
       </c>
-      <c r="B71" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>fitScale = floor + range x fitness/100, applied to every stat in the race, at every fitness</t>
+      <c r="B71" s="43" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C71" s="43" t="inlineStr">
+        <is>
+          <t>D13. Was 0.80: at equal ratings a dog at 60 fitness won 1.3% of its races, so the only usable range was 85-100 and nothing ever fell to the threshold</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="43" t="inlineStr">
         <is>
           <t>Fitness multiplier: range</t>
         </is>
       </c>
-      <c r="B72" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Was a literal in simulateRace.ts until v2 Phase A. D13 softens these to 0.90 / 0.10</t>
+      <c r="B72" s="43" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C72" s="43" t="inlineStr">
+        <is>
+          <t>D13. Was 0.20. Flattened, the curve reads from 40 to 100 and the weekly swings below can be big enough to see</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="87" t="inlineStr">
+        <is>
+          <t>Race, Train or Rest (GDD §5.7 — the weekly per-dog state)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="43" t="inlineStr">
+        <is>
+          <t>Fitness: cost of a race</t>
+        </is>
+      </c>
+      <c r="B75" s="43" t="n">
+        <v>25</v>
+      </c>
+      <c r="C75" s="43" t="inlineStr">
+        <is>
+          <t>D13. Was 12. Two weeks racing in three holds station; three does not</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="43" t="inlineStr">
+        <is>
+          <t>Fitness: gain from a training week</t>
+        </is>
+      </c>
+      <c r="B76" s="43" t="n">
+        <v>8</v>
+      </c>
+      <c r="C76" s="43" t="inlineStr">
+        <is>
+          <t>A Train week is work, not a rest</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="43" t="inlineStr">
+        <is>
+          <t>Fitness: gain from a rest week</t>
+        </is>
+      </c>
+      <c r="B77" s="43" t="n">
+        <v>30</v>
+      </c>
+      <c r="C77" s="43" t="inlineStr">
+        <is>
+          <t>Layoff (injured or banned) recovers at this rate too</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="43" t="inlineStr">
+        <is>
+          <t>Fitness: gain from a rest week with a vet</t>
+        </is>
+      </c>
+      <c r="B78" s="43" t="n">
+        <v>40</v>
+      </c>
+      <c r="C78" s="43" t="inlineStr">
+        <is>
+          <t>GDD §8.3: the vet's bonus rides on Rest</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="43" t="inlineStr">
+        <is>
+          <t>Training: plain kibble, minimum stat points</t>
+        </is>
+      </c>
+      <c r="B79" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" s="43" t="inlineStr">
+        <is>
+          <t>GDD §8.2 placeholder until Phase C builds the feeds. A Train week on kibble alone</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="43" t="inlineStr">
+        <is>
+          <t>Training: plain kibble, maximum stat points</t>
+        </is>
+      </c>
+      <c r="B80" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="C80" s="43" t="inlineStr">
+        <is>
+          <t>is the floor of improvement, +1-3 to one stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="87" t="inlineStr">
+        <is>
+          <t>Growth and decline by age (GDD §5.6 / D14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="43" t="inlineStr">
+        <is>
+          <t>Growth: stat points a week at age 1</t>
+        </is>
+      </c>
+      <c r="B82" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="C82" s="43" t="inlineStr">
+        <is>
+          <t>Replaces v1's +1 every second week at any age up to 2. This is what makes a pup a pup</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="43" t="inlineStr">
+        <is>
+          <t>Growth: stat points a week at age 2</t>
+        </is>
+      </c>
+      <c r="B83" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" s="43" t="inlineStr">
+        <is>
+          <t>Ages 3 and 4 neither grow nor decline</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="43" t="inlineStr">
+        <is>
+          <t>Decline: stat points a week at age 5+</t>
+        </is>
+      </c>
+      <c r="B84" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C84" s="43" t="inlineStr">
+        <is>
+          <t>Subtracted, every week rather than every second</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="43" t="inlineStr">
+        <is>
+          <t>Kennel slots at the top ship tier</t>
+        </is>
+      </c>
+      <c r="B85" s="43" t="n">
+        <v>6</v>
+      </c>
+      <c r="C85" s="43" t="inlineStr">
+        <is>
+          <t>Was 5. Five dogs is what fills a 3-race card (§6.3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="87" t="inlineStr">
+        <is>
+          <t>Local dogs (GDD §6.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Local dog fitness</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>75</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>A planet's own runner turns up fresh but not perfect. v1 left locals on createDog's default 90, which cost nothing when campaigning stables raced at 96 and is a standing handicap now that §5.7 puts them at 60-80</t>
         </is>
       </c>
     </row>

--- a/design/space_dog_racing_economy.xlsx
+++ b/design/space_dog_racing_economy.xlsx
@@ -876,7 +876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D68"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="42" customWidth="1" style="43" min="1" max="1"/>
@@ -1649,144 +1649,181 @@
           <t>Race simulation (GDD §6.2 — the v2 rebalance, 11 September 2026)</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="43" t="inlineStr">
         <is>
           <t>Rebalanced so all four stats matter: measured +10-to-one-stat win rates move from speed 28.8 / stam 16.7 / accel 14.4 / trap 14.0 to rating-weight order, and track length starts to matter at all. D12.</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="43" t="inlineStr">
         <is>
           <t>Race: base speed (m/s)</t>
         </is>
       </c>
-      <c r="B60" t="n">
+      <c r="B60" s="43" t="n">
         <v>13.75</v>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="43" t="inlineStr">
         <is>
           <t>Was 13. The floor every dog runs at before its Speed stat</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="43" t="inlineStr">
         <is>
           <t>Race: speed coefficient (m/s per 100 Speed)</t>
         </is>
       </c>
-      <c r="B61" t="n">
+      <c r="B61" s="43" t="n">
         <v>4.5</v>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="43" t="inlineStr">
         <is>
           <t>Was 6. Cutting this is what stops the race being a pure Speed contest</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="43" t="inlineStr">
         <is>
           <t>Race: fade penalty past the stamina point</t>
         </is>
       </c>
-      <c r="B62" t="n">
+      <c r="B62" s="43" t="n">
         <v>0.5</v>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="43" t="inlineStr">
         <is>
           <t>Was 0.35. Makes Stamina the second-biggest stat, and biggest on a stayer</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="43" t="inlineStr">
         <is>
           <t>Race: acceleration base (m/s²)</t>
         </is>
       </c>
-      <c r="B63" t="n">
+      <c r="B63" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="43" t="inlineStr">
         <is>
           <t>Was 4. Less free acceleration, so the stat buys more</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="43" t="inlineStr">
         <is>
           <t>Race: acceleration coefficient (m/s² per 100 Accel)</t>
         </is>
       </c>
-      <c r="B64" t="n">
+      <c r="B64" s="43" t="n">
         <v>5.5</v>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="43" t="inlineStr">
         <is>
           <t>Was 6. Accel now peaks on the 350 m sprints</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="43" t="inlineStr">
         <is>
           <t>Race: break from the boxes (metres at 100 Trap)</t>
         </is>
       </c>
-      <c r="B65" t="n">
+      <c r="B65" s="43" t="n">
         <v>7</v>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="43" t="inlineStr">
         <is>
           <t>Was 3. Trap craft has to be worth something out of the gate</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="43" t="inlineStr">
         <is>
           <t>Race: bump chance on a bend</t>
         </is>
       </c>
-      <c r="B66" t="n">
+      <c r="B66" s="43" t="n">
         <v>0.3</v>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="43" t="inlineStr">
         <is>
           <t>Was 0.10. The other half of what Trap buys</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="43" t="inlineStr">
         <is>
           <t>Race: bump speed penalty</t>
         </is>
       </c>
-      <c r="B67" t="n">
+      <c r="B67" s="43" t="n">
         <v>0.3</v>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="43" t="inlineStr">
         <is>
           <t>Was 0.15</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="43" t="inlineStr">
         <is>
           <t>Race: bump distance (metres)</t>
         </is>
       </c>
-      <c r="B68" t="n">
+      <c r="B68" s="43" t="n">
         <v>1.2</v>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="43" t="inlineStr">
         <is>
           <t>Was 0.6. Dogs this close on a bend may clash</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="87" t="inlineStr">
+        <is>
+          <t>Condition (GDD §5.2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Fitness multiplier: floor</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>fitScale = floor + range x fitness/100, applied to every stat in the race, at every fitness</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Fitness multiplier: range</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Was a literal in simulateRace.ts until v2 Phase A. D13 softens these to 0.90 / 0.10</t>
         </is>
       </c>
     </row>

--- a/design/space_dog_racing_economy.xlsx
+++ b/design/space_dog_racing_economy.xlsx
@@ -876,7 +876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="42" customWidth="1" style="43" min="1" max="1"/>
@@ -996,13 +996,13 @@
     <row r="9" ht="15" customHeight="1" s="44">
       <c r="A9" s="47" t="inlineStr">
         <is>
-          <t>Standard weekend purses (1st / 2nd / 3rd)</t>
+          <t>Weekend purses (1st / 2nd / 3rd) — GDD §6.4</t>
         </is>
       </c>
       <c r="B9" s="50" t="n"/>
       <c r="C9" s="50" t="inlineStr">
         <is>
-          <t>Bronze and Silver lifted, Gold trimmed in the M4 balance pass (2026-09-08)</t>
+          <t>The Open plus two drawn types (D2). Landed at the old pool: the Open takes the old Gold and each drawn race the mean of the old Bronze and Silver, so the card could be measured before the cut was sized</t>
         </is>
       </c>
       <c r="D9" s="50" t="n"/>
@@ -1010,11 +1010,11 @@
     <row r="10" ht="15" customHeight="1" s="44">
       <c r="A10" s="46" t="inlineStr">
         <is>
-          <t>Bronze 1st</t>
+          <t>The Open 1st</t>
         </is>
       </c>
       <c r="B10" s="55" t="n">
-        <v>1800</v>
+        <v>5800</v>
       </c>
       <c r="C10" s="52" t="n"/>
       <c r="D10" s="50" t="n"/>
@@ -1022,11 +1022,11 @@
     <row r="11" ht="15" customHeight="1" s="44">
       <c r="A11" s="46" t="inlineStr">
         <is>
-          <t>Bronze 2nd</t>
+          <t>The Open 2nd</t>
         </is>
       </c>
       <c r="B11" s="55" t="n">
-        <v>900</v>
+        <v>2900</v>
       </c>
       <c r="C11" s="52" t="n"/>
       <c r="D11" s="50" t="n"/>
@@ -1034,11 +1034,11 @@
     <row r="12" ht="15" customHeight="1" s="44">
       <c r="A12" s="46" t="inlineStr">
         <is>
-          <t>Bronze 3rd</t>
+          <t>The Open 3rd</t>
         </is>
       </c>
       <c r="B12" s="55" t="n">
-        <v>450</v>
+        <v>1450</v>
       </c>
       <c r="C12" s="52" t="n"/>
       <c r="D12" s="50" t="n"/>
@@ -1046,11 +1046,11 @@
     <row r="13" ht="15" customHeight="1" s="44">
       <c r="A13" s="46" t="inlineStr">
         <is>
-          <t>Silver 1st</t>
+          <t>Drawn race 1st</t>
         </is>
       </c>
       <c r="B13" s="55" t="n">
-        <v>3400</v>
+        <v>2600</v>
       </c>
       <c r="C13" s="52" t="n"/>
       <c r="D13" s="50" t="n"/>
@@ -1058,11 +1058,11 @@
     <row r="14" ht="15" customHeight="1" s="44">
       <c r="A14" s="46" t="inlineStr">
         <is>
-          <t>Silver 2nd</t>
+          <t>Drawn race 2nd</t>
         </is>
       </c>
       <c r="B14" s="55" t="n">
-        <v>1700</v>
+        <v>1300</v>
       </c>
       <c r="C14" s="52" t="n"/>
       <c r="D14" s="50" t="n"/>
@@ -1070,11 +1070,11 @@
     <row r="15" ht="15" customHeight="1" s="44">
       <c r="A15" s="46" t="inlineStr">
         <is>
-          <t>Silver 3rd</t>
+          <t>Drawn race 3rd</t>
         </is>
       </c>
       <c r="B15" s="55" t="n">
-        <v>850</v>
+        <v>650</v>
       </c>
       <c r="C15" s="52" t="n"/>
       <c r="D15" s="50" t="n"/>
@@ -1082,79 +1082,65 @@
     <row r="16" ht="15" customHeight="1" s="44">
       <c r="A16" s="46" t="inlineStr">
         <is>
-          <t>Gold 1st</t>
-        </is>
-      </c>
-      <c r="B16" s="56" t="n">
-        <v>5800</v>
-      </c>
-      <c r="C16" s="52" t="n"/>
+          <t>Race card entry criteria (GDD §6.3)</t>
+        </is>
+      </c>
+      <c r="B16" s="56" t="n"/>
+      <c r="C16" s="52" t="inlineStr">
+        <is>
+          <t>Five of the seven types gate on a fact a player cannot suppress — age, wins, runs, last week. These two are the posted numbers</t>
+        </is>
+      </c>
       <c r="D16" s="50" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1" s="44">
       <c r="A17" s="46" t="inlineStr">
         <is>
-          <t>Gold 2nd</t>
+          <t>Handicap: max rating</t>
         </is>
       </c>
       <c r="B17" s="55" t="n">
-        <v>2900</v>
-      </c>
-      <c r="C17" s="52" t="n"/>
+        <v>45</v>
+      </c>
+      <c r="C17" s="52" t="inlineStr">
+        <is>
+          <t>A dog rated above this cannot drop into the Handicap. 55 was measured and rejected: cardCoverage 97.5% made it a race every stable could always fill, which asks nothing</t>
+        </is>
+      </c>
       <c r="D17" s="50" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1" s="44">
       <c r="A18" s="46" t="inlineStr">
         <is>
-          <t>Gold 3rd</t>
+          <t>Invitational: min rating</t>
         </is>
       </c>
       <c r="B18" s="55" t="n">
-        <v>1450</v>
-      </c>
-      <c r="C18" s="52" t="n"/>
+        <v>48</v>
+      </c>
+      <c r="C18" s="52" t="inlineStr">
+        <is>
+          <t>The good-dogs race. At 55 only 12.5% of stable-weekends had a qualifying fit dog and players took 1.2% of its entries — a race the locals owned. 48 lifts coverage to 46%</t>
+        </is>
+      </c>
       <c r="D18" s="50" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1" s="44">
-      <c r="A19" s="47" t="inlineStr">
-        <is>
-          <t>Class eligibility (rating caps — dogs may always race UP a class)</t>
-        </is>
-      </c>
+      <c r="A19" s="47" t="n"/>
       <c r="B19" s="50" t="n"/>
       <c r="C19" s="50" t="n"/>
       <c r="D19" s="50" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1" s="44">
-      <c r="A20" s="46" t="inlineStr">
-        <is>
-          <t>Bronze: max rating</t>
-        </is>
-      </c>
-      <c r="B20" s="57" t="n">
-        <v>45</v>
-      </c>
-      <c r="C20" s="52" t="inlineStr">
-        <is>
-          <t>A dog rated above this cannot sandbag into Bronze</t>
-        </is>
-      </c>
+      <c r="A20" s="46" t="n"/>
+      <c r="B20" s="57" t="n"/>
+      <c r="C20" s="52" t="n"/>
       <c r="D20" s="50" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1" s="44">
-      <c r="A21" s="46" t="inlineStr">
-        <is>
-          <t>Silver: max rating</t>
-        </is>
-      </c>
-      <c r="B21" s="57" t="n">
-        <v>70</v>
-      </c>
-      <c r="C21" s="52" t="inlineStr">
-        <is>
-          <t>Gold has no cap</t>
-        </is>
-      </c>
+      <c r="A21" s="46" t="n"/>
+      <c r="B21" s="57" t="n"/>
+      <c r="C21" s="52" t="n"/>
       <c r="D21" s="50" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1" s="44">
@@ -1999,17 +1985,47 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="43" t="inlineStr">
         <is>
           <t>Local dog fitness</t>
         </is>
       </c>
-      <c r="B88" t="n">
+      <c r="B88" s="43" t="n">
         <v>75</v>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C88" s="43" t="inlineStr">
         <is>
           <t>A planet's own runner turns up fresh but not perfect. v1 left locals on createDog's default 90, which cost nothing when campaigning stables raced at 96 and is a standing handicap now that §5.7 puts them at 60-80</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="43" t="inlineStr">
+        <is>
+          <t>Local dog rating: The Open</t>
+        </is>
+      </c>
+      <c r="B89" s="43" t="n">
+        <v>50</v>
+      </c>
+      <c r="C89" s="43" t="inlineStr">
+        <is>
+          <t>The headline race draws the strongest home team</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="43" t="inlineStr">
+        <is>
+          <t>Local dog rating: a drawn race</t>
+        </is>
+      </c>
+      <c r="B90" s="43" t="n">
+        <v>30</v>
+      </c>
+      <c r="C90" s="43" t="inlineStr">
+        <is>
+          <t>Mean of the old Bronze and Silver locals, to be re-fitted against the fill rate</t>
         </is>
       </c>
     </row>

--- a/design/space_dog_racing_economy.xlsx
+++ b/design/space_dog_racing_economy.xlsx
@@ -876,7 +876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D94"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="42" customWidth="1" style="43" min="1" max="1"/>
@@ -2026,6 +2026,48 @@
       <c r="C90" s="43" t="inlineStr">
         <is>
           <t>Mean of the old Bronze and Silver locals, to be re-fitted against the fill rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Information (GDD §9.3 — the fog)</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>The circuit is dark past next week. What you can buy back, and how far it reaches</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Dossier price</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>650</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>GDD §9.2 prices it at roughly hold × 24: a clear buy for a trader with a big hold and a waste of money for a trainer</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Dossier reach (weeks ahead)</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>2</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Next week is free (§9.3), so a dossier buys the week after — one extra leg to plan against</t>
         </is>
       </c>
     </row>

--- a/design/space_dog_racing_economy.xlsx
+++ b/design/space_dog_racing_economy.xlsx
@@ -1126,9 +1126,19 @@
       <c r="D18" s="50" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1" s="44">
-      <c r="A19" s="47" t="n"/>
-      <c r="B19" s="50" t="n"/>
-      <c r="C19" s="50" t="n"/>
+      <c r="A19" s="47" t="inlineStr">
+        <is>
+          <t>Consolation: weekends of eligibility after a losing run</t>
+        </is>
+      </c>
+      <c r="B19" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" s="50" t="inlineStr">
+        <is>
+          <t>GDD Q12. At one weekend the catch-up race was enterable on only 29% of the weekends it ran, because the dog that qualifies is the dog that just raced and is 25 fitness down</t>
+        </is>
+      </c>
       <c r="D19" s="50" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1" s="44">
@@ -2030,42 +2040,42 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="43" t="inlineStr">
         <is>
           <t>Information (GDD §9.3 — the fog)</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C92" s="43" t="inlineStr">
         <is>
           <t>The circuit is dark past next week. What you can buy back, and how far it reaches</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="43" t="inlineStr">
         <is>
           <t>Dossier price</t>
         </is>
       </c>
-      <c r="B93" t="n">
+      <c r="B93" s="43" t="n">
         <v>650</v>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C93" s="43" t="inlineStr">
         <is>
           <t>GDD §9.2 prices it at roughly hold × 24: a clear buy for a trader with a big hold and a waste of money for a trainer</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="43" t="inlineStr">
         <is>
           <t>Dossier reach (weeks ahead)</t>
         </is>
       </c>
-      <c r="B94" t="n">
+      <c r="B94" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C94" s="43" t="inlineStr">
         <is>
           <t>Next week is free (§9.3), so a dossier buys the week after — one extra leg to plan against</t>
         </is>
